--- a/output_boron/boron_Intermediate_henehan_2013.xlsx
+++ b/output_boron/boron_Intermediate_henehan_2013.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="293">
   <si>
     <t>NA</t>
   </si>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">10.1016/j.epsl.2012.12.029</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/boron_isotopes_henehan_2013.xlsx</t>
+    <t xml:space="preserve">boron_isotopes_henehan_2013_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">GeoB1523_1_1_1_5_</t>
   </si>
   <si>
-    <t xml:space="preserve">Gingele, Franz; Kasten, Sabine; Mulitza, Stefan; Rühlemann, Carsten (2000): Age model and isotopes of sediment core GeoB1523-1. PANGAEA, https://doi.org/10.1594/PANGAEA.56532</t>
+    <t xml:space="preserve">Gingele, Franz; Kasten, Sabine; Mulitza, Stefan; Rühlemann, Carsten (2000): Age model and isotopes of sediment core GeoB1523-1. PANGAEA, https://doi.org/10.1594/PANGAEA.56532; added age uncertainty in agreement with LR04</t>
   </si>
   <si>
     <t xml:space="preserve">not known but likely ~170</t>
@@ -1454,37 +1454,73 @@
     <t xml:space="preserve">GeoB1523_1_1_1_10_</t>
   </si>
   <si>
+    <t xml:space="preserve">Gingele, Franz; Kasten, Sabine; Mulitza, Stefan; Rühlemann, Carsten (2000): Age model and isotopes of sediment core GeoB1523-1. PANGAEA, https://doi.org/10.1594/PANGAEA.56532; added age uncertainty in agreement with LR05</t>
+  </si>
+  <si>
     <t xml:space="preserve">GeoB1523_1_1_1_15_</t>
   </si>
   <si>
+    <t xml:space="preserve">Gingele, Franz; Kasten, Sabine; Mulitza, Stefan; Rühlemann, Carsten (2000): Age model and isotopes of sediment core GeoB1523-1. PANGAEA, https://doi.org/10.1594/PANGAEA.56532; added age uncertainty in agreement with LR06</t>
+  </si>
+  <si>
     <t xml:space="preserve">GeoB1523_1_1_1_20_</t>
   </si>
   <si>
+    <t xml:space="preserve">Gingele, Franz; Kasten, Sabine; Mulitza, Stefan; Rühlemann, Carsten (2000): Age model and isotopes of sediment core GeoB1523-1. PANGAEA, https://doi.org/10.1594/PANGAEA.56532; added age uncertainty in agreement with LR07</t>
+  </si>
+  <si>
     <t xml:space="preserve">GeoB1523_1_1_1_25_</t>
   </si>
   <si>
+    <t xml:space="preserve">Gingele, Franz; Kasten, Sabine; Mulitza, Stefan; Rühlemann, Carsten (2000): Age model and isotopes of sediment core GeoB1523-1. PANGAEA, https://doi.org/10.1594/PANGAEA.56532; added age uncertainty in agreement with LR08</t>
+  </si>
+  <si>
     <t xml:space="preserve">GeoB1523_1_1_1_30_</t>
   </si>
   <si>
+    <t xml:space="preserve">Gingele, Franz; Kasten, Sabine; Mulitza, Stefan; Rühlemann, Carsten (2000): Age model and isotopes of sediment core GeoB1523-1. PANGAEA, https://doi.org/10.1594/PANGAEA.56532; added age uncertainty in agreement with LR09</t>
+  </si>
+  <si>
     <t xml:space="preserve">GeoB1523_1_1_1_35_</t>
   </si>
   <si>
+    <t xml:space="preserve">Gingele, Franz; Kasten, Sabine; Mulitza, Stefan; Rühlemann, Carsten (2000): Age model and isotopes of sediment core GeoB1523-1. PANGAEA, https://doi.org/10.1594/PANGAEA.56532; added age uncertainty in agreement with LR10</t>
+  </si>
+  <si>
     <t xml:space="preserve">GeoB1523_1_1_1_40_</t>
   </si>
   <si>
+    <t xml:space="preserve">Gingele, Franz; Kasten, Sabine; Mulitza, Stefan; Rühlemann, Carsten (2000): Age model and isotopes of sediment core GeoB1523-1. PANGAEA, https://doi.org/10.1594/PANGAEA.56532; added age uncertainty in agreement with LR11</t>
+  </si>
+  <si>
     <t xml:space="preserve">GeoB1523_1_1_1_45_</t>
   </si>
   <si>
+    <t xml:space="preserve">Gingele, Franz; Kasten, Sabine; Mulitza, Stefan; Rühlemann, Carsten (2000): Age model and isotopes of sediment core GeoB1523-1. PANGAEA, https://doi.org/10.1594/PANGAEA.56532; added age uncertainty in agreement with LR12</t>
+  </si>
+  <si>
     <t xml:space="preserve">GeoB1523_1_1_1_55_</t>
   </si>
   <si>
+    <t xml:space="preserve">Gingele, Franz; Kasten, Sabine; Mulitza, Stefan; Rühlemann, Carsten (2000): Age model and isotopes of sediment core GeoB1523-1. PANGAEA, https://doi.org/10.1594/PANGAEA.56532; added age uncertainty in agreement with LR13</t>
+  </si>
+  <si>
     <t xml:space="preserve">GeoB1523_1_1_1_65_</t>
   </si>
   <si>
+    <t xml:space="preserve">Gingele, Franz; Kasten, Sabine; Mulitza, Stefan; Rühlemann, Carsten (2000): Age model and isotopes of sediment core GeoB1523-1. PANGAEA, https://doi.org/10.1594/PANGAEA.56532; added age uncertainty in agreement with LR14</t>
+  </si>
+  <si>
     <t xml:space="preserve">GeoB1523_1_1_1_75_</t>
   </si>
   <si>
+    <t xml:space="preserve">Gingele, Franz; Kasten, Sabine; Mulitza, Stefan; Rühlemann, Carsten (2000): Age model and isotopes of sediment core GeoB1523-1. PANGAEA, https://doi.org/10.1594/PANGAEA.56532; added age uncertainty in agreement with LR15</t>
+  </si>
+  <si>
     <t xml:space="preserve">GeoB1523_1_1_1_85_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gingele, Franz; Kasten, Sabine; Mulitza, Stefan; Rühlemann, Carsten (2000): Age model and isotopes of sediment core GeoB1523-1. PANGAEA, https://doi.org/10.1594/PANGAEA.56532; added age uncertainty in agreement with LR16</t>
   </si>
 </sst>
 </file>
@@ -1492,7 +1528,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1552,12 +1588,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1671,7 +1701,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1753,7 +1783,6 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2360,7 +2389,7 @@
       <c r="B5" t="s">
         <v>241</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" t="s">
         <v>242</v>
       </c>
       <c r="D5" t="s">
@@ -2437,7 +2466,7 @@
       <c r="B6" t="s">
         <v>241</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" t="s">
         <v>242</v>
       </c>
       <c r="D6" t="s">
@@ -2514,7 +2543,7 @@
       <c r="B7" t="s">
         <v>241</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" t="s">
         <v>242</v>
       </c>
       <c r="D7" t="s">
@@ -2591,7 +2620,7 @@
       <c r="B8" t="s">
         <v>241</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" t="s">
         <v>242</v>
       </c>
       <c r="D8" t="s">
@@ -2668,7 +2697,7 @@
       <c r="B9" t="s">
         <v>241</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" t="s">
         <v>242</v>
       </c>
       <c r="D9" t="s">
@@ -2745,7 +2774,7 @@
       <c r="B10" t="s">
         <v>241</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" t="s">
         <v>242</v>
       </c>
       <c r="D10" t="s">
@@ -2822,7 +2851,7 @@
       <c r="B11" t="s">
         <v>241</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" t="s">
         <v>242</v>
       </c>
       <c r="D11" t="s">
@@ -2899,7 +2928,7 @@
       <c r="B12" t="s">
         <v>241</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" t="s">
         <v>242</v>
       </c>
       <c r="D12" t="s">
@@ -2976,7 +3005,7 @@
       <c r="B13" t="s">
         <v>241</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" t="s">
         <v>242</v>
       </c>
       <c r="D13" t="s">
@@ -3053,7 +3082,7 @@
       <c r="B14" t="s">
         <v>241</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" t="s">
         <v>242</v>
       </c>
       <c r="D14" t="s">
@@ -3130,7 +3159,7 @@
       <c r="B15" t="s">
         <v>241</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" t="s">
         <v>242</v>
       </c>
       <c r="D15" t="s">
@@ -3207,7 +3236,7 @@
       <c r="B16" t="s">
         <v>241</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" t="s">
         <v>242</v>
       </c>
       <c r="D16" t="s">
@@ -3284,7 +3313,7 @@
       <c r="B17" t="s">
         <v>241</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" t="s">
         <v>242</v>
       </c>
       <c r="D17" t="s">
@@ -3361,7 +3390,7 @@
       <c r="B18" t="s">
         <v>241</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" t="s">
         <v>242</v>
       </c>
       <c r="D18" t="s">
@@ -3438,7 +3467,7 @@
       <c r="B19" t="s">
         <v>241</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" t="s">
         <v>242</v>
       </c>
       <c r="D19" t="s">
@@ -3515,7 +3544,7 @@
       <c r="B20" t="s">
         <v>241</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" t="s">
         <v>242</v>
       </c>
       <c r="D20" t="s">
@@ -3592,7 +3621,7 @@
       <c r="B21" t="s">
         <v>241</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" t="s">
         <v>242</v>
       </c>
       <c r="D21" t="s">
@@ -3669,7 +3698,7 @@
       <c r="B22" t="s">
         <v>241</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" t="s">
         <v>242</v>
       </c>
       <c r="D22" t="s">
@@ -3746,7 +3775,7 @@
       <c r="B23" t="s">
         <v>241</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" t="s">
         <v>242</v>
       </c>
       <c r="D23" t="s">
@@ -3823,7 +3852,7 @@
       <c r="B24" t="s">
         <v>241</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" t="s">
         <v>242</v>
       </c>
       <c r="D24" t="s">
@@ -3851,7 +3880,7 @@
         <v>#N/A</v>
       </c>
       <c r="L24" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M24" t="s">
         <v>246</v>
@@ -3895,12 +3924,12 @@
     </row>
     <row r="25" ht="19" customHeight="1">
       <c r="A25" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B25" t="s">
         <v>241</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" t="s">
         <v>242</v>
       </c>
       <c r="D25" t="s">
@@ -3928,7 +3957,7 @@
         <v>#N/A</v>
       </c>
       <c r="L25" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="M25" t="s">
         <v>246</v>
@@ -3972,12 +4001,12 @@
     </row>
     <row r="26" ht="19" customHeight="1">
       <c r="A26" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B26" t="s">
         <v>241</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="C26" t="s">
         <v>242</v>
       </c>
       <c r="D26" t="s">
@@ -4005,7 +4034,7 @@
         <v>#N/A</v>
       </c>
       <c r="L26" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="M26" t="s">
         <v>246</v>
@@ -4049,12 +4078,12 @@
     </row>
     <row r="27" ht="19" customHeight="1">
       <c r="A27" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B27" t="s">
         <v>241</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" t="s">
         <v>242</v>
       </c>
       <c r="D27" t="s">
@@ -4082,7 +4111,7 @@
         <v>#N/A</v>
       </c>
       <c r="L27" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="M27" t="s">
         <v>246</v>
@@ -4126,12 +4155,12 @@
     </row>
     <row r="28" ht="19" customHeight="1">
       <c r="A28" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B28" t="s">
         <v>241</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" t="s">
         <v>242</v>
       </c>
       <c r="D28" t="s">
@@ -4159,7 +4188,7 @@
         <v>#N/A</v>
       </c>
       <c r="L28" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="M28" t="s">
         <v>246</v>
@@ -4203,12 +4232,12 @@
     </row>
     <row r="29" ht="19" customHeight="1">
       <c r="A29" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B29" t="s">
         <v>241</v>
       </c>
-      <c r="C29" s="29" t="s">
+      <c r="C29" t="s">
         <v>242</v>
       </c>
       <c r="D29" t="s">
@@ -4236,7 +4265,7 @@
         <v>#N/A</v>
       </c>
       <c r="L29" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="M29" t="s">
         <v>246</v>
@@ -4280,12 +4309,12 @@
     </row>
     <row r="30" ht="19" customHeight="1">
       <c r="A30" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B30" t="s">
         <v>241</v>
       </c>
-      <c r="C30" s="29" t="s">
+      <c r="C30" t="s">
         <v>242</v>
       </c>
       <c r="D30" t="s">
@@ -4313,7 +4342,7 @@
         <v>#N/A</v>
       </c>
       <c r="L30" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="M30" t="s">
         <v>246</v>
@@ -4357,12 +4386,12 @@
     </row>
     <row r="31" ht="19" customHeight="1">
       <c r="A31" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B31" t="s">
         <v>241</v>
       </c>
-      <c r="C31" s="29" t="s">
+      <c r="C31" t="s">
         <v>242</v>
       </c>
       <c r="D31" t="s">
@@ -4390,7 +4419,7 @@
         <v>#N/A</v>
       </c>
       <c r="L31" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="M31" t="s">
         <v>246</v>
@@ -4434,12 +4463,12 @@
     </row>
     <row r="32" ht="19" customHeight="1">
       <c r="A32" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B32" t="s">
         <v>241</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C32" t="s">
         <v>242</v>
       </c>
       <c r="D32" t="s">
@@ -4467,7 +4496,7 @@
         <v>#N/A</v>
       </c>
       <c r="L32" t="s">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="M32" t="s">
         <v>246</v>
@@ -4511,12 +4540,12 @@
     </row>
     <row r="33" ht="19" customHeight="1">
       <c r="A33" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="B33" t="s">
         <v>241</v>
       </c>
-      <c r="C33" s="29" t="s">
+      <c r="C33" t="s">
         <v>242</v>
       </c>
       <c r="D33" t="s">
@@ -4544,7 +4573,7 @@
         <v>#N/A</v>
       </c>
       <c r="L33" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="M33" t="s">
         <v>246</v>
@@ -4588,12 +4617,12 @@
     </row>
     <row r="34" ht="19" customHeight="1">
       <c r="A34" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="B34" t="s">
         <v>241</v>
       </c>
-      <c r="C34" s="29" t="s">
+      <c r="C34" t="s">
         <v>242</v>
       </c>
       <c r="D34" t="s">
@@ -4621,7 +4650,7 @@
         <v>#N/A</v>
       </c>
       <c r="L34" t="s">
-        <v>266</v>
+        <v>290</v>
       </c>
       <c r="M34" t="s">
         <v>246</v>
@@ -4665,12 +4694,12 @@
     </row>
     <row r="35" ht="19" customHeight="1">
       <c r="A35" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="B35" t="s">
         <v>241</v>
       </c>
-      <c r="C35" s="29" t="s">
+      <c r="C35" t="s">
         <v>242</v>
       </c>
       <c r="D35" t="s">
@@ -4698,7 +4727,7 @@
         <v>#N/A</v>
       </c>
       <c r="L35" t="s">
-        <v>266</v>
+        <v>292</v>
       </c>
       <c r="M35" t="s">
         <v>246</v>
@@ -4959,39 +4988,6 @@
       <formula>#REF!="no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1h"/>
-    <hyperlink ref="C6" r:id="rId2h"/>
-    <hyperlink ref="C7" r:id="rId3h"/>
-    <hyperlink ref="C8" r:id="rId4h"/>
-    <hyperlink ref="C9" r:id="rId5h"/>
-    <hyperlink ref="C10" r:id="rId6h"/>
-    <hyperlink ref="C11" r:id="rId7h"/>
-    <hyperlink ref="C12" r:id="rId8h"/>
-    <hyperlink ref="C13" r:id="rId9h"/>
-    <hyperlink ref="C14" r:id="rId10h"/>
-    <hyperlink ref="C15" r:id="rId11h"/>
-    <hyperlink ref="C16" r:id="rId12h"/>
-    <hyperlink ref="C17" r:id="rId13h"/>
-    <hyperlink ref="C18" r:id="rId14h"/>
-    <hyperlink ref="C19" r:id="rId15h"/>
-    <hyperlink ref="C20" r:id="rId16h"/>
-    <hyperlink ref="C21" r:id="rId17h"/>
-    <hyperlink ref="C22" r:id="rId18h"/>
-    <hyperlink ref="C23" r:id="rId19h"/>
-    <hyperlink ref="C24" r:id="rId20h"/>
-    <hyperlink ref="C25" r:id="rId21h"/>
-    <hyperlink ref="C26" r:id="rId22h"/>
-    <hyperlink ref="C27" r:id="rId23h"/>
-    <hyperlink ref="C28" r:id="rId24h"/>
-    <hyperlink ref="C29" r:id="rId25h"/>
-    <hyperlink ref="C30" r:id="rId26h"/>
-    <hyperlink ref="C31" r:id="rId27h"/>
-    <hyperlink ref="C32" r:id="rId28h"/>
-    <hyperlink ref="C33" r:id="rId29h"/>
-    <hyperlink ref="C34" r:id="rId30h"/>
-    <hyperlink ref="C35" r:id="rId31h"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
